--- a/docs/reports/NCR_Kavach_Unified_KPI_Jun22-Jun28.xlsx
+++ b/docs/reports/NCR_Kavach_Unified_KPI_Jun22-Jun28.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,13 +207,13 @@
     <xf numFmtId="3" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,7 +229,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -244,7 +244,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -259,7 +259,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -303,6 +303,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -708,7 +726,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -851,19 +868,19 @@
         <f>'Daily Breakdown'!J214</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="44">
         <f>IFERROR(G5/D5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="45">
         <f>IFERROR(G5/E5,0)</f>
         <v/>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="46">
         <f>IFERROR(G5/E5*100,0)</f>
         <v/>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="45">
         <f>IFERROR(G5/(D5*E5/1000),0)</f>
         <v/>
       </c>
@@ -871,19 +888,19 @@
         <f>'Daily Breakdown'!K214</f>
         <v/>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="44">
         <f>IFERROR(N5/D5,0)</f>
         <v/>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="45">
         <f>IFERROR(N5/E5,0)</f>
         <v/>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="45">
         <f>IFERROR(N5/(D5*E5/100),0)</f>
         <v/>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="46">
         <f>IFERROR(N5/E5*100,0)</f>
         <v/>
       </c>
@@ -933,7 +950,13 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>Availability base excludes locos with FS+OS pkts = 0 (they are still listed; only the Total-pkts availability base drops them).</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1005,7 +1028,7 @@
       <c r="C4" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="47" t="n">
         <v>77.83</v>
       </c>
       <c r="E4" s="18" t="n">
@@ -1045,7 +1068,7 @@
       <c r="C5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E5" s="18" t="n">
@@ -1085,7 +1108,7 @@
       <c r="C6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E6" s="18" t="n">
@@ -1125,7 +1148,7 @@
       <c r="C7" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="47" t="n">
         <v>77.8</v>
       </c>
       <c r="E7" s="18" t="n">
@@ -1165,7 +1188,7 @@
       <c r="C8" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E8" s="18" t="n">
@@ -1205,7 +1228,7 @@
       <c r="C9" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E9" s="18" t="n">
@@ -1245,7 +1268,7 @@
       <c r="C10" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="47" t="n">
         <v>77.7</v>
       </c>
       <c r="E10" s="18" t="n">
@@ -1285,7 +1308,7 @@
       <c r="C11" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="47" t="n">
         <v>77.67</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -1325,7 +1348,7 @@
       <c r="C12" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -1365,7 +1388,7 @@
       <c r="C13" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="47" t="n">
         <v>77.81</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -1405,7 +1428,7 @@
       <c r="C14" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="47" t="n">
         <v>77.68000000000001</v>
       </c>
       <c r="E14" s="18" t="n">
@@ -1445,7 +1468,7 @@
       <c r="C15" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E15" s="18" t="n">
@@ -1485,7 +1508,7 @@
       <c r="C16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="47" t="n">
         <v>77.64</v>
       </c>
       <c r="E16" s="18" t="n">
@@ -1525,7 +1548,7 @@
       <c r="C17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="47" t="n">
         <v>77.81</v>
       </c>
       <c r="E17" s="18" t="n">
@@ -1565,7 +1588,7 @@
       <c r="C18" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E18" s="18" t="n">
@@ -1605,7 +1628,7 @@
       <c r="C19" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="47" t="n">
         <v>77.68000000000001</v>
       </c>
       <c r="E19" s="18" t="n">
@@ -1645,7 +1668,7 @@
       <c r="C20" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="47" t="n">
         <v>77.63</v>
       </c>
       <c r="E20" s="18" t="n">
@@ -1685,7 +1708,7 @@
       <c r="C21" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E21" s="18" t="n">
@@ -1725,7 +1748,7 @@
       <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E22" s="18" t="n">
@@ -1765,7 +1788,7 @@
       <c r="C23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E23" s="18" t="n">
@@ -1805,7 +1828,7 @@
       <c r="C24" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="47" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E24" s="18" t="n">
@@ -1845,7 +1868,7 @@
       <c r="C25" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E25" s="18" t="n">
@@ -1885,7 +1908,7 @@
       <c r="C26" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="47" t="n">
         <v>77.83</v>
       </c>
       <c r="E26" s="18" t="n">
@@ -1925,7 +1948,7 @@
       <c r="C27" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="18" t="n">
@@ -1965,7 +1988,7 @@
       <c r="C28" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="47" t="n">
         <v>27.74</v>
       </c>
       <c r="E28" s="18" t="n">
@@ -2005,7 +2028,7 @@
       <c r="C29" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="47" t="n">
         <v>74.75</v>
       </c>
       <c r="E29" s="18" t="n">
@@ -2046,7 +2069,7 @@
         <f>SUM(C4:C29)</f>
         <v/>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="48">
         <f>SUM(D4:D29)</f>
         <v/>
       </c>
@@ -2055,7 +2078,7 @@
         <v/>
       </c>
       <c r="F30" s="23">
-        <f>SUM(F4:F29)</f>
+        <f>SUMIF(E4:E29,"&gt;0",F4:F29)</f>
         <v/>
       </c>
       <c r="G30" s="24">
@@ -2093,7 +2116,7 @@
       <c r="C31" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E31" s="18" t="n">
@@ -2133,7 +2156,7 @@
       <c r="C32" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E32" s="18" t="n">
@@ -2173,7 +2196,7 @@
       <c r="C33" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E33" s="18" t="n">
@@ -2213,7 +2236,7 @@
       <c r="C34" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E34" s="18" t="n">
@@ -2253,7 +2276,7 @@
       <c r="C35" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E35" s="18" t="n">
@@ -2293,7 +2316,7 @@
       <c r="C36" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E36" s="18" t="n">
@@ -2333,7 +2356,7 @@
       <c r="C37" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="17" t="n">
+      <c r="D37" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E37" s="18" t="n">
@@ -2373,7 +2396,7 @@
       <c r="C38" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="47" t="n">
         <v>77.83</v>
       </c>
       <c r="E38" s="18" t="n">
@@ -2413,7 +2436,7 @@
       <c r="C39" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D39" s="47" t="n">
         <v>77.73999999999999</v>
       </c>
       <c r="E39" s="18" t="n">
@@ -2453,7 +2476,7 @@
       <c r="C40" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D40" s="17" t="n">
+      <c r="D40" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E40" s="18" t="n">
@@ -2493,7 +2516,7 @@
       <c r="C41" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="17" t="n">
+      <c r="D41" s="47" t="n">
         <v>77.73999999999999</v>
       </c>
       <c r="E41" s="18" t="n">
@@ -2533,7 +2556,7 @@
       <c r="C42" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D42" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="18" t="n">
@@ -2573,7 +2596,7 @@
       <c r="C43" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="17" t="n">
+      <c r="D43" s="47" t="n">
         <v>77.73</v>
       </c>
       <c r="E43" s="18" t="n">
@@ -2613,7 +2636,7 @@
       <c r="C44" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="17" t="n">
+      <c r="D44" s="47" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E44" s="18" t="n">
@@ -2653,7 +2676,7 @@
       <c r="C45" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="17" t="n">
+      <c r="D45" s="47" t="n">
         <v>77.8</v>
       </c>
       <c r="E45" s="18" t="n">
@@ -2693,7 +2716,7 @@
       <c r="C46" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="17" t="n">
+      <c r="D46" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E46" s="18" t="n">
@@ -2733,7 +2756,7 @@
       <c r="C47" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="17" t="n">
+      <c r="D47" s="47" t="n">
         <v>77.73999999999999</v>
       </c>
       <c r="E47" s="18" t="n">
@@ -2773,7 +2796,7 @@
       <c r="C48" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D48" s="17" t="n">
+      <c r="D48" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E48" s="18" t="n">
@@ -2813,7 +2836,7 @@
       <c r="C49" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="17" t="n">
+      <c r="D49" s="47" t="n">
         <v>77.81</v>
       </c>
       <c r="E49" s="18" t="n">
@@ -2853,7 +2876,7 @@
       <c r="C50" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="17" t="n">
+      <c r="D50" s="47" t="n">
         <v>77.72</v>
       </c>
       <c r="E50" s="18" t="n">
@@ -2893,7 +2916,7 @@
       <c r="C51" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="17" t="n">
+      <c r="D51" s="47" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E51" s="18" t="n">
@@ -2933,7 +2956,7 @@
       <c r="C52" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="17" t="n">
+      <c r="D52" s="47" t="n">
         <v>50.06</v>
       </c>
       <c r="E52" s="18" t="n">
@@ -2973,7 +2996,7 @@
       <c r="C53" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D53" s="17" t="n">
+      <c r="D53" s="47" t="n">
         <v>41.51</v>
       </c>
       <c r="E53" s="18" t="n">
@@ -3013,7 +3036,7 @@
       <c r="C54" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D54" s="17" t="n">
+      <c r="D54" s="47" t="n">
         <v>27.71</v>
       </c>
       <c r="E54" s="18" t="n">
@@ -3053,7 +3076,7 @@
       <c r="C55" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D55" s="17" t="n">
+      <c r="D55" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E55" s="18" t="n">
@@ -3093,7 +3116,7 @@
       <c r="C56" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D56" s="17" t="n">
+      <c r="D56" s="47" t="n">
         <v>77.73</v>
       </c>
       <c r="E56" s="18" t="n">
@@ -3133,7 +3156,7 @@
       <c r="C57" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D57" s="17" t="n">
+      <c r="D57" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E57" s="18" t="n">
@@ -3173,7 +3196,7 @@
       <c r="C58" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D58" s="17" t="n">
+      <c r="D58" s="47" t="n">
         <v>14.14</v>
       </c>
       <c r="E58" s="18" t="n">
@@ -3214,7 +3237,7 @@
         <f>SUM(C31:C58)</f>
         <v/>
       </c>
-      <c r="D59" s="22">
+      <c r="D59" s="48">
         <f>SUM(D31:D58)</f>
         <v/>
       </c>
@@ -3223,7 +3246,7 @@
         <v/>
       </c>
       <c r="F59" s="23">
-        <f>SUM(F31:F58)</f>
+        <f>SUMIF(E31:E58,"&gt;0",F31:F58)</f>
         <v/>
       </c>
       <c r="G59" s="24">
@@ -3261,7 +3284,7 @@
       <c r="C60" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D60" s="17" t="n">
+      <c r="D60" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E60" s="18" t="n">
@@ -3301,7 +3324,7 @@
       <c r="C61" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D61" s="17" t="n">
+      <c r="D61" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E61" s="18" t="n">
@@ -3341,7 +3364,7 @@
       <c r="C62" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D62" s="17" t="n">
+      <c r="D62" s="47" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E62" s="18" t="n">
@@ -3381,7 +3404,7 @@
       <c r="C63" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D63" s="17" t="n">
+      <c r="D63" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E63" s="18" t="n">
@@ -3421,7 +3444,7 @@
       <c r="C64" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D64" s="17" t="n">
+      <c r="D64" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E64" s="18" t="n">
@@ -3461,7 +3484,7 @@
       <c r="C65" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D65" s="17" t="n">
+      <c r="D65" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E65" s="18" t="n">
@@ -3501,7 +3524,7 @@
       <c r="C66" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D66" s="17" t="n">
+      <c r="D66" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E66" s="18" t="n">
@@ -3541,7 +3564,7 @@
       <c r="C67" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D67" s="17" t="n">
+      <c r="D67" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E67" s="18" t="n">
@@ -3581,7 +3604,7 @@
       <c r="C68" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D68" s="17" t="n">
+      <c r="D68" s="47" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E68" s="18" t="n">
@@ -3621,7 +3644,7 @@
       <c r="C69" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D69" s="17" t="n">
+      <c r="D69" s="47" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E69" s="18" t="n">
@@ -3661,7 +3684,7 @@
       <c r="C70" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D70" s="17" t="n">
+      <c r="D70" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E70" s="18" t="n">
@@ -3701,7 +3724,7 @@
       <c r="C71" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D71" s="17" t="n">
+      <c r="D71" s="47" t="n">
         <v>77.72</v>
       </c>
       <c r="E71" s="18" t="n">
@@ -3741,7 +3764,7 @@
       <c r="C72" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D72" s="17" t="n">
+      <c r="D72" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E72" s="18" t="n">
@@ -3781,7 +3804,7 @@
       <c r="C73" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D73" s="17" t="n">
+      <c r="D73" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E73" s="18" t="n">
@@ -3821,7 +3844,7 @@
       <c r="C74" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D74" s="17" t="n">
+      <c r="D74" s="47" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E74" s="18" t="n">
@@ -3861,7 +3884,7 @@
       <c r="C75" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D75" s="17" t="n">
+      <c r="D75" s="47" t="n">
         <v>77.69</v>
       </c>
       <c r="E75" s="18" t="n">
@@ -3901,7 +3924,7 @@
       <c r="C76" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D76" s="17" t="n">
+      <c r="D76" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E76" s="18" t="n">
@@ -3941,7 +3964,7 @@
       <c r="C77" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D77" s="17" t="n">
+      <c r="D77" s="47" t="n">
         <v>77.7</v>
       </c>
       <c r="E77" s="18" t="n">
@@ -3981,7 +4004,7 @@
       <c r="C78" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D78" s="17" t="n">
+      <c r="D78" s="47" t="n">
         <v>77.72</v>
       </c>
       <c r="E78" s="18" t="n">
@@ -4021,7 +4044,7 @@
       <c r="C79" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D79" s="17" t="n">
+      <c r="D79" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E79" s="18" t="n">
@@ -4061,7 +4084,7 @@
       <c r="C80" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D80" s="17" t="n">
+      <c r="D80" s="47" t="n">
         <v>73.73999999999999</v>
       </c>
       <c r="E80" s="18" t="n">
@@ -4101,7 +4124,7 @@
       <c r="C81" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D81" s="17" t="n">
+      <c r="D81" s="47" t="n">
         <v>36.35</v>
       </c>
       <c r="E81" s="18" t="n">
@@ -4141,7 +4164,7 @@
       <c r="C82" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D82" s="17" t="n">
+      <c r="D82" s="47" t="n">
         <v>22.13</v>
       </c>
       <c r="E82" s="18" t="n">
@@ -4181,7 +4204,7 @@
       <c r="C83" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D83" s="17" t="n">
+      <c r="D83" s="47" t="n">
         <v>40.12</v>
       </c>
       <c r="E83" s="18" t="n">
@@ -4221,7 +4244,7 @@
       <c r="C84" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D84" s="17" t="n">
+      <c r="D84" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E84" s="18" t="n">
@@ -4261,7 +4284,7 @@
       <c r="C85" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D85" s="17" t="n">
+      <c r="D85" s="47" t="n">
         <v>9.32</v>
       </c>
       <c r="E85" s="18" t="n">
@@ -4302,7 +4325,7 @@
         <f>SUM(C60:C85)</f>
         <v/>
       </c>
-      <c r="D86" s="22">
+      <c r="D86" s="48">
         <f>SUM(D60:D85)</f>
         <v/>
       </c>
@@ -4311,7 +4334,7 @@
         <v/>
       </c>
       <c r="F86" s="23">
-        <f>SUM(F60:F85)</f>
+        <f>SUMIF(E60:E85,"&gt;0",F60:F85)</f>
         <v/>
       </c>
       <c r="G86" s="24">
@@ -4349,7 +4372,7 @@
       <c r="C87" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D87" s="17" t="n">
+      <c r="D87" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E87" s="18" t="n">
@@ -4389,7 +4412,7 @@
       <c r="C88" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D88" s="17" t="n">
+      <c r="D88" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E88" s="18" t="n">
@@ -4429,7 +4452,7 @@
       <c r="C89" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D89" s="17" t="n">
+      <c r="D89" s="47" t="n">
         <v>77.83</v>
       </c>
       <c r="E89" s="18" t="n">
@@ -4469,7 +4492,7 @@
       <c r="C90" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D90" s="17" t="n">
+      <c r="D90" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E90" s="18" t="n">
@@ -4509,7 +4532,7 @@
       <c r="C91" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D91" s="17" t="n">
+      <c r="D91" s="47" t="n">
         <v>77.7</v>
       </c>
       <c r="E91" s="18" t="n">
@@ -4549,7 +4572,7 @@
       <c r="C92" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D92" s="17" t="n">
+      <c r="D92" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E92" s="18" t="n">
@@ -4589,7 +4612,7 @@
       <c r="C93" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D93" s="17" t="n">
+      <c r="D93" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E93" s="18" t="n">
@@ -4629,7 +4652,7 @@
       <c r="C94" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D94" s="17" t="n">
+      <c r="D94" s="47" t="n">
         <v>77.83</v>
       </c>
       <c r="E94" s="18" t="n">
@@ -4669,7 +4692,7 @@
       <c r="C95" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D95" s="17" t="n">
+      <c r="D95" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E95" s="18" t="n">
@@ -4709,7 +4732,7 @@
       <c r="C96" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D96" s="17" t="n">
+      <c r="D96" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E96" s="18" t="n">
@@ -4749,7 +4772,7 @@
       <c r="C97" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D97" s="17" t="n">
+      <c r="D97" s="47" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E97" s="18" t="n">
@@ -4789,7 +4812,7 @@
       <c r="C98" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D98" s="17" t="n">
+      <c r="D98" s="47" t="n">
         <v>77.67</v>
       </c>
       <c r="E98" s="18" t="n">
@@ -4829,7 +4852,7 @@
       <c r="C99" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D99" s="17" t="n">
+      <c r="D99" s="47" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E99" s="18" t="n">
@@ -4869,7 +4892,7 @@
       <c r="C100" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D100" s="17" t="n">
+      <c r="D100" s="47" t="n">
         <v>77.83</v>
       </c>
       <c r="E100" s="18" t="n">
@@ -4909,7 +4932,7 @@
       <c r="C101" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D101" s="17" t="n">
+      <c r="D101" s="47" t="n">
         <v>77.8</v>
       </c>
       <c r="E101" s="18" t="n">
@@ -4949,7 +4972,7 @@
       <c r="C102" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D102" s="17" t="n">
+      <c r="D102" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E102" s="18" t="n">
@@ -4989,7 +5012,7 @@
       <c r="C103" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D103" s="17" t="n">
+      <c r="D103" s="47" t="n">
         <v>77.72</v>
       </c>
       <c r="E103" s="18" t="n">
@@ -5029,7 +5052,7 @@
       <c r="C104" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D104" s="17" t="n">
+      <c r="D104" s="47" t="n">
         <v>77.81</v>
       </c>
       <c r="E104" s="18" t="n">
@@ -5069,7 +5092,7 @@
       <c r="C105" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D105" s="17" t="n">
+      <c r="D105" s="47" t="n">
         <v>27.54</v>
       </c>
       <c r="E105" s="18" t="n">
@@ -5109,7 +5132,7 @@
       <c r="C106" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D106" s="17" t="n">
+      <c r="D106" s="47" t="n">
         <v>18.8</v>
       </c>
       <c r="E106" s="18" t="n">
@@ -5149,7 +5172,7 @@
       <c r="C107" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D107" s="17" t="n">
+      <c r="D107" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E107" s="18" t="n">
@@ -5189,7 +5212,7 @@
       <c r="C108" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D108" s="17" t="n">
+      <c r="D108" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E108" s="18" t="n">
@@ -5229,7 +5252,7 @@
       <c r="C109" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D109" s="17" t="n">
+      <c r="D109" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E109" s="18" t="n">
@@ -5269,7 +5292,7 @@
       <c r="C110" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D110" s="17" t="n">
+      <c r="D110" s="47" t="n">
         <v>24.13</v>
       </c>
       <c r="E110" s="18" t="n">
@@ -5309,7 +5332,7 @@
       <c r="C111" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D111" s="17" t="n">
+      <c r="D111" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E111" s="18" t="n">
@@ -5349,7 +5372,7 @@
       <c r="C112" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="17" t="n">
+      <c r="D112" s="47" t="n">
         <v>4.08</v>
       </c>
       <c r="E112" s="18" t="n">
@@ -5389,7 +5412,7 @@
       <c r="C113" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="17" t="n">
+      <c r="D113" s="47" t="n">
         <v>1.45</v>
       </c>
       <c r="E113" s="18" t="n">
@@ -5430,7 +5453,7 @@
         <f>SUM(C87:C113)</f>
         <v/>
       </c>
-      <c r="D114" s="22">
+      <c r="D114" s="48">
         <f>SUM(D87:D113)</f>
         <v/>
       </c>
@@ -5439,7 +5462,7 @@
         <v/>
       </c>
       <c r="F114" s="23">
-        <f>SUM(F87:F113)</f>
+        <f>SUMIF(E87:E113,"&gt;0",F87:F113)</f>
         <v/>
       </c>
       <c r="G114" s="24">
@@ -5477,7 +5500,7 @@
       <c r="C115" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D115" s="17" t="n">
+      <c r="D115" s="47" t="n">
         <v>77.83</v>
       </c>
       <c r="E115" s="18" t="n">
@@ -5517,7 +5540,7 @@
       <c r="C116" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D116" s="17" t="n">
+      <c r="D116" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E116" s="18" t="n">
@@ -5557,7 +5580,7 @@
       <c r="C117" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D117" s="17" t="n">
+      <c r="D117" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E117" s="18" t="n">
@@ -5597,7 +5620,7 @@
       <c r="C118" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D118" s="17" t="n">
+      <c r="D118" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E118" s="18" t="n">
@@ -5637,7 +5660,7 @@
       <c r="C119" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D119" s="17" t="n">
+      <c r="D119" s="47" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E119" s="18" t="n">
@@ -5677,7 +5700,7 @@
       <c r="C120" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D120" s="17" t="n">
+      <c r="D120" s="47" t="n">
         <v>77.7</v>
       </c>
       <c r="E120" s="18" t="n">
@@ -5717,7 +5740,7 @@
       <c r="C121" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D121" s="17" t="n">
+      <c r="D121" s="47" t="n">
         <v>74.73999999999999</v>
       </c>
       <c r="E121" s="18" t="n">
@@ -5757,7 +5780,7 @@
       <c r="C122" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D122" s="17" t="n">
+      <c r="D122" s="47" t="n">
         <v>77.7</v>
       </c>
       <c r="E122" s="18" t="n">
@@ -5797,7 +5820,7 @@
       <c r="C123" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D123" s="17" t="n">
+      <c r="D123" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E123" s="18" t="n">
@@ -5837,7 +5860,7 @@
       <c r="C124" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D124" s="17" t="n">
+      <c r="D124" s="47" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E124" s="18" t="n">
@@ -5877,7 +5900,7 @@
       <c r="C125" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D125" s="17" t="n">
+      <c r="D125" s="47" t="n">
         <v>77.73999999999999</v>
       </c>
       <c r="E125" s="18" t="n">
@@ -5917,7 +5940,7 @@
       <c r="C126" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D126" s="17" t="n">
+      <c r="D126" s="47" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E126" s="18" t="n">
@@ -5957,7 +5980,7 @@
       <c r="C127" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D127" s="17" t="n">
+      <c r="D127" s="47" t="n">
         <v>68.44</v>
       </c>
       <c r="E127" s="18" t="n">
@@ -5997,7 +6020,7 @@
       <c r="C128" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D128" s="17" t="n">
+      <c r="D128" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E128" s="18" t="n">
@@ -6037,7 +6060,7 @@
       <c r="C129" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D129" s="17" t="n">
+      <c r="D129" s="47" t="n">
         <v>77.83</v>
       </c>
       <c r="E129" s="18" t="n">
@@ -6077,7 +6100,7 @@
       <c r="C130" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D130" s="17" t="n">
+      <c r="D130" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E130" s="18" t="n">
@@ -6117,7 +6140,7 @@
       <c r="C131" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D131" s="17" t="n">
+      <c r="D131" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E131" s="18" t="n">
@@ -6157,7 +6180,7 @@
       <c r="C132" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D132" s="17" t="n">
+      <c r="D132" s="47" t="n">
         <v>77.61</v>
       </c>
       <c r="E132" s="18" t="n">
@@ -6197,7 +6220,7 @@
       <c r="C133" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D133" s="17" t="n">
+      <c r="D133" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E133" s="18" t="n">
@@ -6237,7 +6260,7 @@
       <c r="C134" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D134" s="17" t="n">
+      <c r="D134" s="47" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E134" s="18" t="n">
@@ -6277,7 +6300,7 @@
       <c r="C135" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D135" s="17" t="n">
+      <c r="D135" s="47" t="n">
         <v>77.67</v>
       </c>
       <c r="E135" s="18" t="n">
@@ -6317,7 +6340,7 @@
       <c r="C136" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D136" s="17" t="n">
+      <c r="D136" s="47" t="n">
         <v>77.73</v>
       </c>
       <c r="E136" s="18" t="n">
@@ -6357,7 +6380,7 @@
       <c r="C137" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D137" s="17" t="n">
+      <c r="D137" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E137" s="18" t="n">
@@ -6397,7 +6420,7 @@
       <c r="C138" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D138" s="17" t="n">
+      <c r="D138" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E138" s="18" t="n">
@@ -6437,7 +6460,7 @@
       <c r="C139" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D139" s="17" t="n">
+      <c r="D139" s="47" t="n">
         <v>73.72</v>
       </c>
       <c r="E139" s="18" t="n">
@@ -6477,7 +6500,7 @@
       <c r="C140" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D140" s="17" t="n">
+      <c r="D140" s="47" t="n">
         <v>77.72</v>
       </c>
       <c r="E140" s="18" t="n">
@@ -6517,7 +6540,7 @@
       <c r="C141" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D141" s="17" t="n">
+      <c r="D141" s="47" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="E141" s="18" t="n">
@@ -6557,7 +6580,7 @@
       <c r="C142" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D142" s="17" t="n">
+      <c r="D142" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E142" s="18" t="n">
@@ -6597,7 +6620,7 @@
       <c r="C143" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D143" s="17" t="n">
+      <c r="D143" s="47" t="n">
         <v>77.69</v>
       </c>
       <c r="E143" s="18" t="n">
@@ -6637,7 +6660,7 @@
       <c r="C144" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D144" s="17" t="n">
+      <c r="D144" s="47" t="n">
         <v>74.2</v>
       </c>
       <c r="E144" s="18" t="n">
@@ -6677,7 +6700,7 @@
       <c r="C145" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D145" s="17" t="n">
+      <c r="D145" s="47" t="n">
         <v>72.67</v>
       </c>
       <c r="E145" s="18" t="n">
@@ -6717,7 +6740,7 @@
       <c r="C146" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D146" s="17" t="n">
+      <c r="D146" s="47" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="E146" s="18" t="n">
@@ -6758,7 +6781,7 @@
         <f>SUM(C115:C146)</f>
         <v/>
       </c>
-      <c r="D147" s="22">
+      <c r="D147" s="48">
         <f>SUM(D115:D146)</f>
         <v/>
       </c>
@@ -6767,7 +6790,7 @@
         <v/>
       </c>
       <c r="F147" s="23">
-        <f>SUM(F115:F146)</f>
+        <f>SUMIF(E115:E146,"&gt;0",F115:F146)</f>
         <v/>
       </c>
       <c r="G147" s="24">
@@ -6805,7 +6828,7 @@
       <c r="C148" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D148" s="17" t="n">
+      <c r="D148" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E148" s="18" t="n">
@@ -6845,7 +6868,7 @@
       <c r="C149" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D149" s="17" t="n">
+      <c r="D149" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E149" s="18" t="n">
@@ -6885,7 +6908,7 @@
       <c r="C150" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D150" s="17" t="n">
+      <c r="D150" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E150" s="18" t="n">
@@ -6925,7 +6948,7 @@
       <c r="C151" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D151" s="17" t="n">
+      <c r="D151" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E151" s="18" t="n">
@@ -6965,7 +6988,7 @@
       <c r="C152" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D152" s="17" t="n">
+      <c r="D152" s="47" t="n">
         <v>77.73</v>
       </c>
       <c r="E152" s="18" t="n">
@@ -7005,7 +7028,7 @@
       <c r="C153" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D153" s="17" t="n">
+      <c r="D153" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E153" s="18" t="n">
@@ -7045,7 +7068,7 @@
       <c r="C154" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D154" s="17" t="n">
+      <c r="D154" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E154" s="18" t="n">
@@ -7085,7 +7108,7 @@
       <c r="C155" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D155" s="17" t="n">
+      <c r="D155" s="47" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E155" s="18" t="n">
@@ -7125,7 +7148,7 @@
       <c r="C156" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D156" s="17" t="n">
+      <c r="D156" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E156" s="18" t="n">
@@ -7165,7 +7188,7 @@
       <c r="C157" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D157" s="17" t="n">
+      <c r="D157" s="47" t="n">
         <v>77.69</v>
       </c>
       <c r="E157" s="18" t="n">
@@ -7205,7 +7228,7 @@
       <c r="C158" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D158" s="17" t="n">
+      <c r="D158" s="47" t="n">
         <v>77.72</v>
       </c>
       <c r="E158" s="18" t="n">
@@ -7245,7 +7268,7 @@
       <c r="C159" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D159" s="17" t="n">
+      <c r="D159" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E159" s="18" t="n">
@@ -7285,7 +7308,7 @@
       <c r="C160" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D160" s="17" t="n">
+      <c r="D160" s="47" t="n">
         <v>77.81</v>
       </c>
       <c r="E160" s="18" t="n">
@@ -7325,7 +7348,7 @@
       <c r="C161" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D161" s="17" t="n">
+      <c r="D161" s="47" t="n">
         <v>77.73999999999999</v>
       </c>
       <c r="E161" s="18" t="n">
@@ -7365,7 +7388,7 @@
       <c r="C162" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D162" s="17" t="n">
+      <c r="D162" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E162" s="18" t="n">
@@ -7405,7 +7428,7 @@
       <c r="C163" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D163" s="17" t="n">
+      <c r="D163" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E163" s="18" t="n">
@@ -7445,7 +7468,7 @@
       <c r="C164" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D164" s="17" t="n">
+      <c r="D164" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E164" s="18" t="n">
@@ -7485,7 +7508,7 @@
       <c r="C165" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D165" s="17" t="n">
+      <c r="D165" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E165" s="18" t="n">
@@ -7525,7 +7548,7 @@
       <c r="C166" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D166" s="17" t="n">
+      <c r="D166" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E166" s="18" t="n">
@@ -7565,7 +7588,7 @@
       <c r="C167" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D167" s="17" t="n">
+      <c r="D167" s="47" t="n">
         <v>73.20999999999999</v>
       </c>
       <c r="E167" s="18" t="n">
@@ -7605,7 +7628,7 @@
       <c r="C168" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D168" s="17" t="n">
+      <c r="D168" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E168" s="18" t="n">
@@ -7645,7 +7668,7 @@
       <c r="C169" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D169" s="17" t="n">
+      <c r="D169" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E169" s="18" t="n">
@@ -7685,7 +7708,7 @@
       <c r="C170" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D170" s="17" t="n">
+      <c r="D170" s="47" t="n">
         <v>77.72</v>
       </c>
       <c r="E170" s="18" t="n">
@@ -7725,7 +7748,7 @@
       <c r="C171" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D171" s="17" t="n">
+      <c r="D171" s="47" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E171" s="18" t="n">
@@ -7765,7 +7788,7 @@
       <c r="C172" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D172" s="17" t="n">
+      <c r="D172" s="47" t="n">
         <v>77.65000000000001</v>
       </c>
       <c r="E172" s="18" t="n">
@@ -7805,7 +7828,7 @@
       <c r="C173" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D173" s="17" t="n">
+      <c r="D173" s="47" t="n">
         <v>77.73</v>
       </c>
       <c r="E173" s="18" t="n">
@@ -7845,7 +7868,7 @@
       <c r="C174" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D174" s="17" t="n">
+      <c r="D174" s="47" t="n">
         <v>77.83</v>
       </c>
       <c r="E174" s="18" t="n">
@@ -7885,7 +7908,7 @@
       <c r="C175" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D175" s="17" t="n">
+      <c r="D175" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E175" s="18" t="n">
@@ -7925,7 +7948,7 @@
       <c r="C176" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D176" s="17" t="n">
+      <c r="D176" s="47" t="n">
         <v>40.97</v>
       </c>
       <c r="E176" s="18" t="n">
@@ -7965,7 +7988,7 @@
       <c r="C177" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D177" s="17" t="n">
+      <c r="D177" s="47" t="n">
         <v>18.5</v>
       </c>
       <c r="E177" s="18" t="n">
@@ -8005,7 +8028,7 @@
       <c r="C178" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D178" s="17" t="n">
+      <c r="D178" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E178" s="18" t="n">
@@ -8045,7 +8068,7 @@
       <c r="C179" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D179" s="17" t="n">
+      <c r="D179" s="47" t="n">
         <v>8.59</v>
       </c>
       <c r="E179" s="18" t="n">
@@ -8085,7 +8108,7 @@
       <c r="C180" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D180" s="17" t="n">
+      <c r="D180" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E180" s="18" t="n">
@@ -8125,7 +8148,7 @@
       <c r="C181" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D181" s="17" t="n">
+      <c r="D181" s="47" t="n">
         <v>9.07</v>
       </c>
       <c r="E181" s="18" t="n">
@@ -8166,7 +8189,7 @@
         <f>SUM(C148:C181)</f>
         <v/>
       </c>
-      <c r="D182" s="22">
+      <c r="D182" s="48">
         <f>SUM(D148:D181)</f>
         <v/>
       </c>
@@ -8175,7 +8198,7 @@
         <v/>
       </c>
       <c r="F182" s="23">
-        <f>SUM(F148:F181)</f>
+        <f>SUMIF(E148:E181,"&gt;0",F148:F181)</f>
         <v/>
       </c>
       <c r="G182" s="24">
@@ -8213,7 +8236,7 @@
       <c r="C183" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D183" s="17" t="n">
+      <c r="D183" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E183" s="18" t="n">
@@ -8253,7 +8276,7 @@
       <c r="C184" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D184" s="17" t="n">
+      <c r="D184" s="47" t="n">
         <v>77.73</v>
       </c>
       <c r="E184" s="18" t="n">
@@ -8293,7 +8316,7 @@
       <c r="C185" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D185" s="17" t="n">
+      <c r="D185" s="47" t="n">
         <v>77.75</v>
       </c>
       <c r="E185" s="18" t="n">
@@ -8333,7 +8356,7 @@
       <c r="C186" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D186" s="17" t="n">
+      <c r="D186" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E186" s="18" t="n">
@@ -8373,7 +8396,7 @@
       <c r="C187" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D187" s="17" t="n">
+      <c r="D187" s="47" t="n">
         <v>77.72</v>
       </c>
       <c r="E187" s="18" t="n">
@@ -8413,7 +8436,7 @@
       <c r="C188" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D188" s="17" t="n">
+      <c r="D188" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E188" s="18" t="n">
@@ -8453,7 +8476,7 @@
       <c r="C189" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D189" s="17" t="n">
+      <c r="D189" s="47" t="n">
         <v>77.67</v>
       </c>
       <c r="E189" s="18" t="n">
@@ -8493,7 +8516,7 @@
       <c r="C190" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D190" s="17" t="n">
+      <c r="D190" s="47" t="n">
         <v>77.72</v>
       </c>
       <c r="E190" s="18" t="n">
@@ -8533,7 +8556,7 @@
       <c r="C191" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D191" s="17" t="n">
+      <c r="D191" s="47" t="n">
         <v>77.86</v>
       </c>
       <c r="E191" s="18" t="n">
@@ -8573,7 +8596,7 @@
       <c r="C192" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D192" s="17" t="n">
+      <c r="D192" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E192" s="18" t="n">
@@ -8613,7 +8636,7 @@
       <c r="C193" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D193" s="17" t="n">
+      <c r="D193" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E193" s="18" t="n">
@@ -8653,7 +8676,7 @@
       <c r="C194" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D194" s="17" t="n">
+      <c r="D194" s="47" t="n">
         <v>77.62</v>
       </c>
       <c r="E194" s="18" t="n">
@@ -8693,7 +8716,7 @@
       <c r="C195" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D195" s="17" t="n">
+      <c r="D195" s="47" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E195" s="18" t="n">
@@ -8733,7 +8756,7 @@
       <c r="C196" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D196" s="17" t="n">
+      <c r="D196" s="47" t="n">
         <v>77.8</v>
       </c>
       <c r="E196" s="18" t="n">
@@ -8773,7 +8796,7 @@
       <c r="C197" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D197" s="17" t="n">
+      <c r="D197" s="47" t="n">
         <v>77.7</v>
       </c>
       <c r="E197" s="18" t="n">
@@ -8813,7 +8836,7 @@
       <c r="C198" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D198" s="17" t="n">
+      <c r="D198" s="47" t="n">
         <v>77.72</v>
       </c>
       <c r="E198" s="18" t="n">
@@ -8853,7 +8876,7 @@
       <c r="C199" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D199" s="17" t="n">
+      <c r="D199" s="47" t="n">
         <v>77.87</v>
       </c>
       <c r="E199" s="18" t="n">
@@ -8893,7 +8916,7 @@
       <c r="C200" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D200" s="17" t="n">
+      <c r="D200" s="47" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E200" s="18" t="n">
@@ -8933,7 +8956,7 @@
       <c r="C201" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D201" s="17" t="n">
+      <c r="D201" s="47" t="n">
         <v>77.73</v>
       </c>
       <c r="E201" s="18" t="n">
@@ -8973,7 +8996,7 @@
       <c r="C202" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D202" s="17" t="n">
+      <c r="D202" s="47" t="n">
         <v>77.84</v>
       </c>
       <c r="E202" s="18" t="n">
@@ -9013,7 +9036,7 @@
       <c r="C203" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D203" s="17" t="n">
+      <c r="D203" s="47" t="n">
         <v>77.81</v>
       </c>
       <c r="E203" s="18" t="n">
@@ -9053,7 +9076,7 @@
       <c r="C204" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D204" s="17" t="n">
+      <c r="D204" s="47" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E204" s="18" t="n">
@@ -9093,7 +9116,7 @@
       <c r="C205" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D205" s="17" t="n">
+      <c r="D205" s="47" t="n">
         <v>77.72</v>
       </c>
       <c r="E205" s="18" t="n">
@@ -9133,7 +9156,7 @@
       <c r="C206" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D206" s="17" t="n">
+      <c r="D206" s="47" t="n">
         <v>66.88</v>
       </c>
       <c r="E206" s="18" t="n">
@@ -9173,7 +9196,7 @@
       <c r="C207" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D207" s="17" t="n">
+      <c r="D207" s="47" t="n">
         <v>19.39</v>
       </c>
       <c r="E207" s="18" t="n">
@@ -9213,7 +9236,7 @@
       <c r="C208" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D208" s="17" t="n">
+      <c r="D208" s="47" t="n">
         <v>51.83</v>
       </c>
       <c r="E208" s="18" t="n">
@@ -9253,7 +9276,7 @@
       <c r="C209" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D209" s="17" t="n">
+      <c r="D209" s="47" t="n">
         <v>36.87</v>
       </c>
       <c r="E209" s="18" t="n">
@@ -9293,7 +9316,7 @@
       <c r="C210" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D210" s="17" t="n">
+      <c r="D210" s="47" t="n">
         <v>18.93</v>
       </c>
       <c r="E210" s="18" t="n">
@@ -9333,7 +9356,7 @@
       <c r="C211" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D211" s="17" t="n">
+      <c r="D211" s="47" t="n">
         <v>6.79</v>
       </c>
       <c r="E211" s="18" t="n">
@@ -9373,7 +9396,7 @@
       <c r="C212" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D212" s="17" t="n">
+      <c r="D212" s="47" t="n">
         <v>19.11</v>
       </c>
       <c r="E212" s="18" t="n">
@@ -9414,7 +9437,7 @@
         <f>SUM(C183:C212)</f>
         <v/>
       </c>
-      <c r="D213" s="22">
+      <c r="D213" s="48">
         <f>SUM(D183:D212)</f>
         <v/>
       </c>
@@ -9423,7 +9446,7 @@
         <v/>
       </c>
       <c r="F213" s="23">
-        <f>SUM(F183:F212)</f>
+        <f>SUMIF(E183:E212,"&gt;0",F183:F212)</f>
         <v/>
       </c>
       <c r="G213" s="24">
@@ -9458,7 +9481,7 @@
         <f>C30+C59+C86+C114+C147+C182+C213</f>
         <v/>
       </c>
-      <c r="D214" s="27">
+      <c r="D214" s="49">
         <f>D30+D59+D86+D114+D147+D182+D213</f>
         <v/>
       </c>
@@ -9534,7 +9557,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="30" t="inlineStr">
         <is>
@@ -9542,7 +9564,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -21870,7 +21891,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -32277,7 +32297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="B1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -32292,7 +32312,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="34" customHeight="1">
       <c r="B3" s="42" t="inlineStr">
         <is>

--- a/docs/reports/NCR_Kavach_Unified_KPI_Jun22-Jun28.xlsx
+++ b/docs/reports/NCR_Kavach_Unified_KPI_Jun22-Jun28.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10063,7 +10063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L214"/>
+  <dimension ref="A1:M214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10141,6 +10141,11 @@
           <t>Valid Trip?</t>
         </is>
       </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>Loco Travel</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -10197,6 +10202,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -10253,6 +10263,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -10309,6 +10324,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -10365,6 +10385,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -10421,6 +10446,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -10477,6 +10507,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -10533,6 +10568,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -10589,6 +10629,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -10645,6 +10690,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -10701,6 +10751,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -10757,6 +10812,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -10813,6 +10873,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
@@ -10869,6 +10934,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -10925,6 +10995,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -10981,6 +11056,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -11037,6 +11117,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -11093,6 +11178,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -11149,6 +11239,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -11205,6 +11300,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
@@ -11261,6 +11361,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
@@ -11317,6 +11422,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -11373,6 +11483,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
@@ -11429,6 +11544,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -11485,6 +11605,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
@@ -11541,6 +11666,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -11597,6 +11727,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
@@ -11653,6 +11788,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -11709,6 +11849,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -11765,6 +11910,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -11821,6 +11971,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -11877,6 +12032,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -11933,6 +12093,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -11989,6 +12154,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="34" t="inlineStr">
@@ -12045,6 +12215,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M39" s="16" t="inlineStr">
+        <is>
+          <t>LC545, Chhata, LC540, Ajhai</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="34" t="inlineStr">
@@ -12101,6 +12276,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M40" s="16" t="inlineStr">
+        <is>
+          <t>LC545, Chhata, LC540, Ajhai</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="34" t="inlineStr">
@@ -12157,6 +12337,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>LC545, Chhata, LC540, Ajhai</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="34" t="inlineStr">
@@ -12213,6 +12398,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>LC545, Chhata, LC540, Ajhai</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
@@ -12269,6 +12459,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M43" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
@@ -12325,6 +12520,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -12381,6 +12581,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -12437,6 +12642,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -12493,6 +12703,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
@@ -12549,6 +12764,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
@@ -12605,6 +12825,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M49" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
@@ -12661,6 +12886,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -12717,6 +12947,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M51" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
@@ -12773,6 +13008,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -12829,6 +13069,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -12885,6 +13130,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
@@ -12941,6 +13191,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M55" s="16" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
@@ -12997,6 +13248,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M56" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
@@ -13053,6 +13309,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M57" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
@@ -13109,6 +13370,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M58" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
@@ -13165,6 +13431,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M59" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
@@ -13221,6 +13492,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M60" s="16" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
@@ -13277,6 +13549,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M61" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
@@ -13333,6 +13610,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M62" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -13389,6 +13671,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M63" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -13445,6 +13732,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M64" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
@@ -13501,6 +13793,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M65" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
@@ -13557,6 +13854,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M66" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
@@ -13613,6 +13915,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M67" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
@@ -13669,6 +13976,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M68" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
@@ -13725,6 +14037,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M69" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
@@ -13781,6 +14098,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M70" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
@@ -13837,6 +14159,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M71" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
@@ -13893,6 +14220,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M72" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
@@ -13949,6 +14281,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M73" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
@@ -14005,6 +14342,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M74" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
@@ -14061,6 +14403,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M75" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
@@ -14117,6 +14464,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M76" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
@@ -14173,6 +14525,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M77" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
@@ -14229,6 +14586,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M78" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
@@ -14285,6 +14647,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M79" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="16" t="inlineStr">
@@ -14341,6 +14708,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M80" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
@@ -14397,6 +14769,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M81" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
@@ -14453,6 +14830,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M82" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
@@ -14509,6 +14891,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M83" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
@@ -14565,6 +14952,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M84" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
@@ -14621,6 +15013,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M85" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="16" t="inlineStr">
@@ -14677,6 +15074,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M86" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
@@ -14733,6 +15135,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M87" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
@@ -14789,6 +15196,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M88" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
@@ -14845,6 +15257,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M89" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="16" t="inlineStr">
@@ -14901,6 +15318,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M90" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="16" t="inlineStr">
@@ -14957,6 +15379,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M91" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="16" t="inlineStr">
@@ -15013,6 +15440,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M92" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="16" t="inlineStr">
@@ -15069,6 +15501,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M93" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="16" t="inlineStr">
@@ -15125,6 +15562,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M94" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="16" t="inlineStr">
@@ -15181,6 +15623,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M95" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="16" t="inlineStr">
@@ -15237,6 +15684,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M96" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="16" t="inlineStr">
@@ -15293,6 +15745,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M97" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="16" t="inlineStr">
@@ -15349,6 +15806,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M98" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="16" t="inlineStr">
@@ -15405,6 +15867,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M99" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="16" t="inlineStr">
@@ -15461,6 +15928,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M100" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
@@ -15517,6 +15989,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M101" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="16" t="inlineStr">
@@ -15573,6 +16050,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M102" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
@@ -15629,6 +16111,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M103" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="16" t="inlineStr">
@@ -15685,6 +16172,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M104" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="16" t="inlineStr">
@@ -15741,6 +16233,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M105" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="16" t="inlineStr">
@@ -15797,6 +16294,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M106" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="34" t="inlineStr">
@@ -15853,6 +16355,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M107" s="16" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="34" t="inlineStr">
@@ -15909,6 +16412,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M108" s="16" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="16" t="inlineStr">
@@ -15965,6 +16469,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M109" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
@@ -16021,6 +16530,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M110" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="16" t="inlineStr">
@@ -16077,6 +16591,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M111" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="16" t="inlineStr">
@@ -16133,6 +16652,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M112" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="16" t="inlineStr">
@@ -16189,6 +16713,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M113" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="16" t="inlineStr">
@@ -16245,6 +16774,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M114" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="16" t="inlineStr">
@@ -16301,6 +16835,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M115" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="16" t="inlineStr">
@@ -16357,6 +16896,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M116" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="16" t="inlineStr">
@@ -16413,6 +16957,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M117" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="16" t="inlineStr">
@@ -16469,6 +17018,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M118" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="16" t="inlineStr">
@@ -16525,6 +17079,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M119" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="16" t="inlineStr">
@@ -16581,6 +17140,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M120" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="16" t="inlineStr">
@@ -16637,6 +17201,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M121" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="16" t="inlineStr">
@@ -16693,6 +17262,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M122" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="16" t="inlineStr">
@@ -16749,6 +17323,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M123" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="16" t="inlineStr">
@@ -16805,6 +17384,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M124" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="16" t="inlineStr">
@@ -16861,6 +17445,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M125" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="16" t="inlineStr">
@@ -16917,6 +17506,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M126" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="16" t="inlineStr">
@@ -16973,6 +17567,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M127" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="16" t="inlineStr">
@@ -17029,6 +17628,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M128" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="16" t="inlineStr">
@@ -17085,6 +17689,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M129" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="16" t="inlineStr">
@@ -17141,6 +17750,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M130" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="16" t="inlineStr">
@@ -17197,6 +17811,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M131" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="16" t="inlineStr">
@@ -17253,6 +17872,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M132" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="16" t="inlineStr">
@@ -17309,6 +17933,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M133" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="16" t="inlineStr">
@@ -17365,6 +17994,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M134" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="16" t="inlineStr">
@@ -17421,6 +18055,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M135" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="16" t="inlineStr">
@@ -17477,6 +18116,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M136" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="16" t="inlineStr">
@@ -17533,6 +18177,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M137" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="16" t="inlineStr">
@@ -17589,6 +18238,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M138" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="16" t="inlineStr">
@@ -17645,6 +18299,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M139" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="16" t="inlineStr">
@@ -17701,6 +18360,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M140" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="16" t="inlineStr">
@@ -17757,6 +18421,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M141" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="16" t="inlineStr">
@@ -17813,6 +18482,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M142" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="16" t="inlineStr">
@@ -17869,6 +18543,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M143" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="16" t="inlineStr">
@@ -17925,6 +18604,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M144" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="16" t="inlineStr">
@@ -17981,6 +18665,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M145" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="16" t="inlineStr">
@@ -18037,6 +18726,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M146" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="16" t="inlineStr">
@@ -18093,6 +18787,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M147" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="16" t="inlineStr">
@@ -18149,6 +18848,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M148" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="16" t="inlineStr">
@@ -18205,6 +18909,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M149" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="16" t="inlineStr">
@@ -18261,6 +18970,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M150" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="16" t="inlineStr">
@@ -18317,6 +19031,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M151" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="16" t="inlineStr">
@@ -18373,6 +19092,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M152" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="16" t="inlineStr">
@@ -18429,6 +19153,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M153" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="16" t="inlineStr">
@@ -18485,6 +19214,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M154" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="16" t="inlineStr">
@@ -18541,6 +19275,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M155" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="16" t="inlineStr">
@@ -18597,6 +19336,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M156" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="16" t="inlineStr">
@@ -18653,6 +19397,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M157" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="16" t="inlineStr">
@@ -18709,6 +19458,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M158" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="16" t="inlineStr">
@@ -18765,6 +19519,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M159" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="16" t="inlineStr">
@@ -18821,6 +19580,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M160" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="16" t="inlineStr">
@@ -18877,6 +19641,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M161" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="16" t="inlineStr">
@@ -18933,6 +19702,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M162" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="16" t="inlineStr">
@@ -18989,6 +19763,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M163" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="16" t="inlineStr">
@@ -19045,6 +19824,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M164" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="16" t="inlineStr">
@@ -19101,6 +19885,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M165" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="16" t="inlineStr">
@@ -19157,6 +19946,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M166" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="16" t="inlineStr">
@@ -19213,6 +20007,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M167" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="16" t="inlineStr">
@@ -19269,6 +20068,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M168" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="16" t="inlineStr">
@@ -19325,6 +20129,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M169" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="16" t="inlineStr">
@@ -19381,6 +20190,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M170" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="16" t="inlineStr">
@@ -19437,6 +20251,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M171" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="16" t="inlineStr">
@@ -19493,6 +20312,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M172" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="16" t="inlineStr">
@@ -19549,6 +20373,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M173" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="16" t="inlineStr">
@@ -19605,6 +20434,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M174" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="16" t="inlineStr">
@@ -19661,6 +20495,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M175" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="16" t="inlineStr">
@@ -19717,6 +20556,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M176" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="16" t="inlineStr">
@@ -19773,6 +20617,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M177" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="16" t="inlineStr">
@@ -19829,6 +20678,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M178" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="16" t="inlineStr">
@@ -19885,6 +20739,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M179" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="16" t="inlineStr">
@@ -19941,6 +20800,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M180" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="16" t="inlineStr">
@@ -19997,6 +20861,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M181" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="16" t="inlineStr">
@@ -20053,6 +20922,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M182" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="16" t="inlineStr">
@@ -20109,6 +20983,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M183" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="16" t="inlineStr">
@@ -20165,6 +21044,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M184" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="16" t="inlineStr">
@@ -20221,6 +21105,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M185" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="16" t="inlineStr">
@@ -20277,6 +21166,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M186" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="16" t="inlineStr">
@@ -20333,6 +21227,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M187" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="16" t="inlineStr">
@@ -20389,6 +21288,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M188" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="16" t="inlineStr">
@@ -20445,6 +21349,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M189" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="16" t="inlineStr">
@@ -20501,6 +21410,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M190" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="16" t="inlineStr">
@@ -20557,6 +21471,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M191" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="16" t="inlineStr">
@@ -20613,6 +21532,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M192" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="16" t="inlineStr">
@@ -20669,6 +21593,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M193" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="16" t="inlineStr">
@@ -20725,6 +21654,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M194" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="16" t="inlineStr">
@@ -20781,6 +21715,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M195" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="16" t="inlineStr">
@@ -20837,6 +21776,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M196" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="16" t="inlineStr">
@@ -20893,6 +21837,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M197" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="16" t="inlineStr">
@@ -20949,6 +21898,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M198" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="16" t="inlineStr">
@@ -21005,6 +21959,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M199" s="16" t="inlineStr">
+        <is>
+          <t>LC545, Chhata</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="16" t="inlineStr">
@@ -21061,6 +22020,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M200" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="16" t="inlineStr">
@@ -21117,6 +22081,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M201" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="16" t="inlineStr">
@@ -21173,6 +22142,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M202" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="16" t="inlineStr">
@@ -21229,6 +22203,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M203" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="16" t="inlineStr">
@@ -21285,6 +22264,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M204" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="16" t="inlineStr">
@@ -21341,6 +22325,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M205" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="16" t="inlineStr">
@@ -21397,6 +22386,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M206" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="16" t="inlineStr">
@@ -21453,6 +22447,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M207" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="16" t="inlineStr">
@@ -21509,6 +22508,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M208" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="16" t="inlineStr">
@@ -21565,6 +22569,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M209" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="16" t="inlineStr">
@@ -21621,6 +22630,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M210" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="16" t="inlineStr">
@@ -21677,6 +22691,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M211" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="16" t="inlineStr">
@@ -21733,6 +22752,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M212" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="34" t="inlineStr">
@@ -21789,6 +22813,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M213" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="16" t="inlineStr">
@@ -21843,6 +22872,11 @@
       <c r="L214" s="16" t="inlineStr">
         <is>
           <t>Valid</t>
+        </is>
+      </c>
+      <c r="M214" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
         </is>
       </c>
     </row>
